--- a/results/week5_margin_vs_overload.xlsx
+++ b/results/week5_margin_vs_overload.xlsx
@@ -495,13 +495,13 @@
         <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-23.19456588987669</v>
+        <v>-3.113310879751225</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>13.24838647811576</v>
+        <v>14.22473037517737</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-1.750746472273469</v>
+        <v>-0.2188660732145796</v>
       </c>
     </row>
     <row r="3">
@@ -511,10 +511,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>118063.9112058363</v>
+        <v>118083.9924608464</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>13.24839266959478</v>
+        <v>14.22473656665639</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1</v>
@@ -534,22 +534,22 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>117804.1953103942</v>
+        <v>118031.059456761</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3.031913933500479</v>
+        <v>3.316408373914962</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>259.7158954420884</v>
+        <v>52.93300408535288</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>10.2164787360943</v>
+        <v>10.90832819274143</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>25.42127303848098</v>
+        <v>4.852531309112547</v>
       </c>
     </row>
     <row r="5">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>117735.1809520053</v>
+        <v>117962.9392030903</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>0</v>
@@ -568,13 +568,13 @@
         <v>1</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>328.7302538309305</v>
+        <v>121.0532577560807</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>13.24839266959478</v>
+        <v>14.22473656665639</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>24.81284047274432</v>
+        <v>8.510052695094302</v>
       </c>
     </row>
     <row r="6">
@@ -584,22 +584,22 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>117559.9774612103</v>
+        <v>117532.0804668493</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.9990069176319176</v>
+        <v>0.9990921428571428</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>503.9337446259888</v>
+        <v>551.9119939971279</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>13.24839266959478</v>
+        <v>14.22473656665639</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>38.03734967657795</v>
+        <v>38.79945272876558</v>
       </c>
     </row>
     <row r="7">
@@ -618,13 +618,13 @@
         <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>551.7663036845915</v>
+        <v>571.847558694717</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>13.24839266959478</v>
+        <v>14.22473656665639</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>41.64779210921954</v>
+        <v>40.2009243556159</v>
       </c>
     </row>
     <row r="8">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>117280.7334714507</v>
+        <v>117507.3695490342</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>783.1777343855501</v>
+        <v>576.6229118122137</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>13.24839266959478</v>
+        <v>14.22473656665639</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>59.11492464915781</v>
+        <v>40.53663202198424</v>
       </c>
     </row>
     <row r="9">
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>112313.6295210458</v>
+        <v>112474.2015855492</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>10.2770225705571</v>
+        <v>10.87579645430932</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.9908713319418676</v>
+        <v>0.9909251913265308</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>5750.281684790461</v>
+        <v>5609.790875297171</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>2.971370099037681</v>
+        <v>3.348940112347071</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1935.229033452537</v>
+        <v>1675.094414084821</v>
       </c>
     </row>
     <row r="10">
@@ -684,22 +684,22 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>110459.3635465434</v>
+        <v>110803.5687497603</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>4.303407689872962</v>
+        <v>4.637838178240389</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.98732747670086</v>
+        <v>0.9874354922280888</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>7604.547659292846</v>
+        <v>7280.42371108607</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>8.944984979721818</v>
+        <v>9.586898388416005</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>850.1464984605644</v>
+        <v>759.4138809151372</v>
       </c>
     </row>
     <row r="11">
@@ -709,22 +709,22 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>108150.9238207752</v>
+        <v>108158.6261610442</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>4.413176446667032</v>
+        <v>4.701707339431732</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.984043868903736</v>
+        <v>0.9834479976801568</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>9912.987385061046</v>
+        <v>9925.366299802205</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>8.835216222927748</v>
+        <v>9.52302922722466</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1121.985827504305</v>
+        <v>1042.248854117483</v>
       </c>
     </row>
     <row r="12">
@@ -734,22 +734,22 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>107321.1614938919</v>
+        <v>107872.7926018735</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>9.27543105102653</v>
+        <v>9.274499274318272</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.9825949489333428</v>
+        <v>0.9829554778966288</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>10742.74971194439</v>
+        <v>10211.19985897293</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>3.972961618568251</v>
+        <v>4.95023729233812</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2703.965138182177</v>
+        <v>2062.769773638453</v>
       </c>
     </row>
     <row r="13">
@@ -759,22 +759,22 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>106367.2728027639</v>
+        <v>106681.7648171703</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>4.203328901066482</v>
+        <v>4.483569891284005</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.9801857063442798</v>
+        <v>0.9806806798840628</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>11696.63840307236</v>
+        <v>11402.22764367613</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>9.045063768528298</v>
+        <v>9.741166675372387</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1293.151568899938</v>
+        <v>1170.519715313284</v>
       </c>
     </row>
     <row r="14">
@@ -784,22 +784,22 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>105709.1514136995</v>
+        <v>106340.4351546219</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>4.530573824205209</v>
+        <v>4.98363120662573</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.9793404414038342</v>
+        <v>0.9797995153061224</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>12354.75979213674</v>
+        <v>11743.5573062245</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>8.717818845389571</v>
+        <v>9.241105360030662</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1417.18473522429</v>
+        <v>1270.795738031227</v>
       </c>
     </row>
   </sheetData>
